--- a/artfynd/A 30652-2024 artfynd.xlsx
+++ b/artfynd/A 30652-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,357 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118888359</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8416</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Piltorp (Piltorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>585843</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6577523</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118888323</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8416</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Piltorp (Piltorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>585826</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6577585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118888180</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8405</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Piltorp (Piltorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585796</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6577522</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30652-2024 artfynd.xlsx
+++ b/artfynd/A 30652-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118888359</v>
+        <v>118888323</v>
       </c>
       <c r="B3" t="n">
         <v>8416</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585843</v>
+        <v>585826</v>
       </c>
       <c r="R3" t="n">
-        <v>6577523</v>
+        <v>6577585</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118888323</v>
+        <v>118888180</v>
       </c>
       <c r="B4" t="n">
-        <v>8416</v>
+        <v>8405</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585826</v>
+        <v>585796</v>
       </c>
       <c r="R4" t="n">
-        <v>6577585</v>
+        <v>6577522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118888180</v>
+        <v>118888359</v>
       </c>
       <c r="B5" t="n">
-        <v>8405</v>
+        <v>8416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585796</v>
+        <v>585843</v>
       </c>
       <c r="R5" t="n">
-        <v>6577522</v>
+        <v>6577523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 30652-2024 artfynd.xlsx
+++ b/artfynd/A 30652-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118888323</v>
+        <v>118888359</v>
       </c>
       <c r="B3" t="n">
         <v>8416</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585826</v>
+        <v>585843</v>
       </c>
       <c r="R3" t="n">
-        <v>6577585</v>
+        <v>6577523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118888359</v>
+        <v>118888323</v>
       </c>
       <c r="B5" t="n">
         <v>8416</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585843</v>
+        <v>585826</v>
       </c>
       <c r="R5" t="n">
-        <v>6577523</v>
+        <v>6577585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
